--- a/public/sample/students_import_sample.xlsx
+++ b/public/sample/students_import_sample.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>student_name</t>
   </si>
@@ -22,98 +22,74 @@
     <t>f_name</t>
   </si>
   <si>
-    <t>sno</t>
-  </si>
-  <si>
     <t>email_id</t>
   </si>
   <si>
     <t>contact</t>
   </si>
   <si>
+    <t>college_name</t>
+  </si>
+  <si>
+    <t>session</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>technology</t>
+  </si>
+  <si>
+    <t>total_fees</t>
+  </si>
+  <si>
+    <t>reg_fees</t>
+  </si>
+  <si>
+    <t>duration</t>
+  </si>
+  <si>
+    <t>start_date</t>
+  </si>
+  <si>
+    <t>joined</t>
+  </si>
+  <si>
+    <t>sohan sharma</t>
+  </si>
+  <si>
+    <t>register_date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 Month </t>
+  </si>
+  <si>
     <t>gender</t>
   </si>
   <si>
-    <t>college_name</t>
-  </si>
-  <si>
-    <t>session</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>technology</t>
-  </si>
-  <si>
-    <t>total_fees</t>
-  </si>
-  <si>
-    <t>reg_fees</t>
-  </si>
-  <si>
-    <t>pending_fees</t>
-  </si>
-  <si>
-    <t>next_due_date</t>
-  </si>
-  <si>
-    <t>department</t>
-  </si>
-  <si>
-    <t>join_date</t>
-  </si>
-  <si>
-    <t>duration</t>
-  </si>
-  <si>
-    <t>batch_assign</t>
-  </si>
-  <si>
-    <t>reg_due_amount</t>
-  </si>
-  <si>
-    <t>start_date</t>
-  </si>
-  <si>
-    <t>end_date</t>
-  </si>
-  <si>
-    <t>John Doe</t>
-  </si>
-  <si>
-    <t>Father Name</t>
-  </si>
-  <si>
-    <t>john@example.com11</t>
-  </si>
-  <si>
-    <t>Male</t>
-  </si>
-  <si>
-    <t>First</t>
-  </si>
-  <si>
-    <t>joined</t>
-  </si>
-  <si>
-    <t>Python</t>
-  </si>
-  <si>
-    <t>IT</t>
-  </si>
-  <si>
-    <t>9-11 first batch</t>
-  </si>
-  <si>
-    <t>BGIET</t>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>mohitsharma12@yopmail.com</t>
+  </si>
+  <si>
+    <t>Government Polytechnic College, Mohali,Punjab</t>
+  </si>
+  <si>
+    <t>paid_fees</t>
+  </si>
+  <si>
+    <t>Vipin Sharma</t>
+  </si>
+  <si>
+    <t>php</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -248,6 +224,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="33">
@@ -547,7 +530,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -590,12 +573,20 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -629,6 +620,7 @@
     <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
     <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Hyperlink" xfId="42" builtinId="8"/>
     <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
     <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
@@ -929,10 +921,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="16.33203125" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" customWidth="1"/>
+    <col min="4" max="4" width="32.5546875" customWidth="1"/>
+    <col min="5" max="5" width="31.5546875" customWidth="1"/>
+    <col min="6" max="6" width="44.109375" customWidth="1"/>
+    <col min="7" max="7" width="37.5546875" customWidth="1"/>
+    <col min="9" max="9" width="21.33203125" customWidth="1"/>
+    <col min="10" max="10" width="19" customWidth="1"/>
+    <col min="11" max="11" width="21" customWidth="1"/>
+    <col min="12" max="12" width="42.5546875" customWidth="1"/>
+    <col min="13" max="13" width="27.44140625" customWidth="1"/>
+    <col min="14" max="14" width="44.109375" customWidth="1"/>
+    <col min="15" max="15" width="83" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -940,16 +948,16 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
       </c>
       <c r="G1" t="s">
         <v>6</v>
@@ -964,105 +972,79 @@
         <v>9</v>
       </c>
       <c r="K1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
       <c r="O1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" t="s">
-        <v>20</v>
-      </c>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
         <v>21</v>
       </c>
       <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2">
+        <v>9813298132</v>
+      </c>
+      <c r="F2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" t="s">
         <v>22</v>
       </c>
-      <c r="C2">
-        <v>123</v>
-      </c>
-      <c r="D2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2">
-        <v>98126543210</v>
-      </c>
-      <c r="F2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I2" t="s">
-        <v>26</v>
-      </c>
-      <c r="J2" t="s">
-        <v>27</v>
+      <c r="I2">
+        <v>20000</v>
+      </c>
+      <c r="J2">
+        <v>1000</v>
       </c>
       <c r="K2">
-        <v>50000</v>
+        <v>4000</v>
       </c>
       <c r="L2">
-        <v>10000</v>
-      </c>
-      <c r="M2">
-        <v>40000</v>
-      </c>
-      <c r="N2" s="1">
-        <v>45413</v>
-      </c>
-      <c r="O2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P2" s="1">
+        <v>179</v>
+      </c>
+      <c r="M2" s="1">
         <v>45301</v>
       </c>
-      <c r="Q2">
-        <v>13</v>
-      </c>
-      <c r="R2" t="s">
-        <v>29</v>
-      </c>
-      <c r="S2">
-        <v>5000</v>
-      </c>
-      <c r="T2" s="1">
-        <v>45306</v>
-      </c>
-      <c r="U2" s="1">
-        <v>45488</v>
-      </c>
+      <c r="N2" s="3">
+        <v>45700</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="D3" s="2"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="1"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>